--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.37215049966183</v>
+        <v>3.472974456195047</v>
       </c>
       <c r="D2" t="n">
-        <v>20.75566484231034</v>
+        <v>3.372795536875431</v>
       </c>
       <c r="E2" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F2" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.036092802488294</v>
+        <v>1.305865080404348</v>
       </c>
       <c r="D3" t="n">
-        <v>7.591945144421807</v>
+        <v>1.233691085968544</v>
       </c>
       <c r="E3" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F3" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.43503261215716</v>
+        <v>3.320692799475539</v>
       </c>
       <c r="D4" t="n">
-        <v>20.32199581723867</v>
+        <v>3.302324320301284</v>
       </c>
       <c r="E4" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F4" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.75840572729799</v>
+        <v>4.998240930685923</v>
       </c>
       <c r="D5" t="n">
-        <v>31.46994034632459</v>
+        <v>5.113865306277746</v>
       </c>
       <c r="E5" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F5" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.88169095015039</v>
+        <v>6.318274779399438</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18922567134056</v>
+        <v>2.630749171592841</v>
       </c>
       <c r="E6" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F6" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.44419473905514</v>
+        <v>1.697181645096461</v>
       </c>
       <c r="D7" t="n">
-        <v>9.686055183912975</v>
+        <v>1.573983967385858</v>
       </c>
       <c r="E7" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F7" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.41006835239833</v>
+        <v>2.666636107264729</v>
       </c>
       <c r="D8" t="n">
-        <v>11.37300058045384</v>
+        <v>1.848112594323749</v>
       </c>
       <c r="E8" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F8" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.227341574519162</v>
+        <v>1.174443005859364</v>
       </c>
       <c r="D9" t="n">
-        <v>7.499054164659757</v>
+        <v>1.218596301757211</v>
       </c>
       <c r="E9" t="n">
-        <v>10.48590905507273</v>
+        <v>1.703960221449318</v>
       </c>
       <c r="F9" t="n">
-        <v>7.775569977296917</v>
+        <v>1.263530121310749</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
